--- a/Team-Data/2020-21/12-24-2020-21.xlsx
+++ b/Team-Data/2020-21/12-24-2020-21.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-24-2020-21</t>
+          <t>2020-12-24</t>
         </is>
       </c>
     </row>
